--- a/ig/DM-AOUT-2026/CodeSystem-TRE-R274-ActiviteSanitaireRegulee.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-TRE-R274-ActiviteSanitaireRegulee.xlsx
@@ -457,6 +457,72 @@
     <t>Prélèvement de tissus</t>
   </si>
   <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>Greffe de face ou de face inférieure</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale de main</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>Prélèvement de cellules mononuclées autologues</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Prélèvement de cellules mononuclées allogéniques</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale d'avant-bras</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale de bras</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Greffe de membre inférieur</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>Greffe de langue</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>Greffe de pénis</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Greffe de paroi abdominale</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Greffe de tissus cutanés conjonctifs et vasculo- nerveux</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
@@ -553,6 +619,12 @@
     <t>Prise en charge des patients atteints de sclérose en plaques</t>
   </si>
   <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>Maison de naissance</t>
+  </si>
+  <si>
     <t>T0</t>
   </si>
   <si>
@@ -599,78 +671,6 @@
   </si>
   <si>
     <t>SSRS - Viroses chroniques</t>
-  </si>
-  <si>
-    <t>A8</t>
-  </si>
-  <si>
-    <t>Greffe de face ou de face inférieure</t>
-  </si>
-  <si>
-    <t>A9</t>
-  </si>
-  <si>
-    <t>Greffe unilatérale ou bilatérale de main</t>
-  </si>
-  <si>
-    <t>B0</t>
-  </si>
-  <si>
-    <t>Prélèvement de cellules mononuclées autologues</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>Prélèvement de cellules mononuclées allogéniques</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>Greffe unilatérale ou bilatérale d'avant-bras</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Greffe unilatérale ou bilatérale de bras</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>Greffe de membre inférieur</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>Greffe de langue</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>Greffe de pénis</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>Greffe de paroi abdominale</t>
-  </si>
-  <si>
-    <t>H3</t>
-  </si>
-  <si>
-    <t>Greffe de tissus cutanés conjonctifs et vasculo- nerveux</t>
-  </si>
-  <si>
-    <t>S8</t>
-  </si>
-  <si>
-    <t>Maison de naissance</t>
   </si>
 </sst>
 </file>
